--- a/check_out_forms/003_field_trip_check_out_form--check_out_forms.xlsx
+++ b/check_out_forms/003_field_trip_check_out_form--check_out_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -944,7 +944,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Teacher Name</t>
+          <t>Teacher Name 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -967,7 +967,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Teacher Phone</t>
+          <t>Teacher Phone 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Student Signature</t>
+          <t>Student Signature 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Teacher Signature</t>
+          <t>Teacher Signature 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bus Signature</t>
+          <t>Bus Signature 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Form Submitted By</t>
+          <t>Form Submitted By 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1260,231 +1260,112 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>form_submitted_by_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>form_submitted_by_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>chatjane</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>chatjane</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>form_submitted_by_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>chatdennis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>chatdennis</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>form_submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>form_submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>chatjane</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>chatjane</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>student_grade_choices</t>
+          <t>form_submitted_by_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>chatdennis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>student_grade_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>form_submitted_by_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>form_submitted_by_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>chatjane</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>chatjane</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>form_submitted_by_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>chatdennis</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>chatdennis</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>form_submitted_by_2_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>chatjimmy</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>form_submitted_by_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>chatjane</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>chatjane</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>form_submitted_by_2_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>chatdennis</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
         <is>
           <t>chatdennis</t>
         </is>
